--- a/Dialers Attendance.xlsx
+++ b/Dialers Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29902"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ALL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C9C4AC-0216-47F2-8853-C08B8A97D939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0523F4-6614-44D9-8B0C-18D80A453B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Table1!$A$1:$C$988</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Table1!$A$1:$C$1113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="10">
   <si>
     <t>date</t>
   </si>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -164,6 +164,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -201,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{24112913-5115-4A45-8927-3108FA77D38F}" name="Table1_1" displayName="Table1_1" ref="A1:C988" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C988" xr:uid="{24112913-5115-4A45-8927-3108FA77D38F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{24112913-5115-4A45-8927-3108FA77D38F}" name="Table1_1" displayName="Table1_1" ref="A1:C1113" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C1113" xr:uid="{24112913-5115-4A45-8927-3108FA77D38F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{8F859507-84CB-413F-9284-928F1DC3CFC2}" uniqueName="1" name="date" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{FE2C3BF3-97D2-4FBA-8C8B-F5374DB4B9CB}" uniqueName="2" name="dialer" queryTableFieldId="2" dataDxfId="0"/>
@@ -499,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A336F12-E6EB-444F-B1DE-07B907CCBF0C}">
-  <dimension ref="A1:O988"/>
+  <dimension ref="A1:O1113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -11424,6 +11427,1381 @@
       </c>
       <c r="C988">
         <v>23</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A989" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B989" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C989">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A990" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B990" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C990">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A991" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B991" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C991">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A992" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B992" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C992">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A993" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B993" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C993">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A994" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B994" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C994">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A995" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B995" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C995">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A996" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B996" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C996">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A997" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B997" t="s">
+        <v>9</v>
+      </c>
+      <c r="C997">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A998" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B998" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C998">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A999" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B999" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C999">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1000" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1000" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1000">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1001" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1001">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1002" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1002" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1002">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1003" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1003" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1003">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1004" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1005" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1005" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1005">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1006" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1006" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1006">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1007" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1007">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1008" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1008" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1008">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1009" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1009" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1009">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1010">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1011" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1011">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1012" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1012" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1012">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1013" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1013" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1013">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1014" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1014">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1015" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1015" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1015">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1016" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B1016" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1016">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1017" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1017">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1018" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B1018" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1018">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1019" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B1019" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1019">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1020" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1020">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1021" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B1021" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1021">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1022" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B1022" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1022">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1023" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1023">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1024" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B1024" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1024">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B1025" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1025">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1026" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B1026" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1026">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B1027" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1027">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B1028" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1028">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B1029" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1029">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B1030" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1030">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B1031" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1031">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B1032" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1032">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B1033" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1033">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B1034" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1034">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B1035" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1035">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B1036" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1036">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B1037" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1037">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B1038" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1038">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B1039" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1039">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B1040" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1040">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B1041" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1041">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B1042" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1042">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B1043" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1043">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B1044" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1044">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B1045" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1045">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B1046" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1046">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B1047" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1047">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B1048" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1048">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B1049" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1049">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B1050" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1050">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B1051" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1051">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B1052" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1052">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B1053" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1053">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B1054" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1054">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B1055" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1055">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B1056" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1056">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B1057" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1057">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B1058" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1058">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B1059" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1059">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B1060" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1060">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B1061" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1061">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B1062" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1062">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B1063" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1063">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B1064" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1064">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B1065" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1065">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B1066" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1066">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B1067" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1067">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B1068" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1068">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B1069" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1069">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B1070" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1070">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B1071" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1071">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B1072" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1072">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B1073" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1073">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B1074" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1074">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B1075" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1075">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B1076" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1076">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B1077" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1077">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B1078" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1078">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B1079" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1079">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B1080" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1080">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B1081" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1081">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B1082" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1082">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B1083" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1083">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B1084" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1084">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B1085" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1085">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B1086" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1086">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B1087" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1087">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B1088" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1088">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B1089" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1089">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B1090" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1090">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1091" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B1091" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1091">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1092" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B1092" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1092">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1093" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B1093" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1093">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1094" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B1094" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1094">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1095" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B1095" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1095">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1096" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B1096" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1096">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1097" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B1097" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1097">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1098" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B1098" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1098">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1099" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B1099" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1099">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1100" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B1100" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1100">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1101" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B1101" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1101">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1102" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B1102" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1102">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1103" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B1103" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1103">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1104" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B1104" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1104">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1105" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B1105" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1105">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1106" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B1106" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1106">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1107" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B1107" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1107">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1108" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B1108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1108">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1109" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B1109" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1109">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1110" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B1110" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1110">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1111" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B1111" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1111">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1112" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B1112" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1112">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1113" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B1113" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1113">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Dialers Attendance.xlsx
+++ b/Dialers Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29902"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ALL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oss\Documents\Conor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0523F4-6614-44D9-8B0C-18D80A453B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6032BD9D-220F-4F89-AFC1-BC8E35AE9825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="135" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -164,9 +164,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11818,7 +11815,7 @@
       <c r="A1024" s="1">
         <v>46043</v>
       </c>
-      <c r="B1024" s="7" t="s">
+      <c r="B1024" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1024">
@@ -11829,7 +11826,7 @@
       <c r="A1025" s="1">
         <v>46043</v>
       </c>
-      <c r="B1025" s="8" t="s">
+      <c r="B1025" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C1025">
@@ -11840,7 +11837,7 @@
       <c r="A1026" s="1">
         <v>46043</v>
       </c>
-      <c r="B1026" s="6" t="s">
+      <c r="B1026" t="s">
         <v>9</v>
       </c>
       <c r="C1026">
@@ -11851,7 +11848,7 @@
       <c r="A1027" s="1">
         <v>46044</v>
       </c>
-      <c r="B1027" s="7" t="s">
+      <c r="B1027" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1027">
@@ -11862,7 +11859,7 @@
       <c r="A1028" s="1">
         <v>46044</v>
       </c>
-      <c r="B1028" s="8" t="s">
+      <c r="B1028" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1028">
@@ -11873,7 +11870,7 @@
       <c r="A1029" s="1">
         <v>46044</v>
       </c>
-      <c r="B1029" s="6" t="s">
+      <c r="B1029" t="s">
         <v>9</v>
       </c>
       <c r="C1029">
@@ -11884,7 +11881,7 @@
       <c r="A1030" s="1">
         <v>46045</v>
       </c>
-      <c r="B1030" s="7" t="s">
+      <c r="B1030" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1030">
@@ -11895,7 +11892,7 @@
       <c r="A1031" s="1">
         <v>46045</v>
       </c>
-      <c r="B1031" s="8" t="s">
+      <c r="B1031" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1031">
@@ -11906,7 +11903,7 @@
       <c r="A1032" s="1">
         <v>46045</v>
       </c>
-      <c r="B1032" s="6" t="s">
+      <c r="B1032" t="s">
         <v>9</v>
       </c>
       <c r="C1032">
@@ -11917,7 +11914,7 @@
       <c r="A1033" s="1">
         <v>46048</v>
       </c>
-      <c r="B1033" s="7" t="s">
+      <c r="B1033" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1033">
@@ -11928,7 +11925,7 @@
       <c r="A1034" s="1">
         <v>46048</v>
       </c>
-      <c r="B1034" s="8" t="s">
+      <c r="B1034" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1034">
@@ -11939,7 +11936,7 @@
       <c r="A1035" s="1">
         <v>46048</v>
       </c>
-      <c r="B1035" s="6" t="s">
+      <c r="B1035" t="s">
         <v>9</v>
       </c>
       <c r="C1035">
@@ -11950,7 +11947,7 @@
       <c r="A1036" s="1">
         <v>46049</v>
       </c>
-      <c r="B1036" s="7" t="s">
+      <c r="B1036" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1036">
@@ -11961,7 +11958,7 @@
       <c r="A1037" s="1">
         <v>46049</v>
       </c>
-      <c r="B1037" s="8" t="s">
+      <c r="B1037" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1037">
@@ -11972,7 +11969,7 @@
       <c r="A1038" s="1">
         <v>46049</v>
       </c>
-      <c r="B1038" s="6" t="s">
+      <c r="B1038" t="s">
         <v>9</v>
       </c>
       <c r="C1038">
@@ -11983,7 +11980,7 @@
       <c r="A1039" s="1">
         <v>46050</v>
       </c>
-      <c r="B1039" s="7" t="s">
+      <c r="B1039" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1039">
@@ -11994,7 +11991,7 @@
       <c r="A1040" s="1">
         <v>46050</v>
       </c>
-      <c r="B1040" s="8" t="s">
+      <c r="B1040" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1040">
@@ -12005,7 +12002,7 @@
       <c r="A1041" s="1">
         <v>46050</v>
       </c>
-      <c r="B1041" s="6" t="s">
+      <c r="B1041" t="s">
         <v>9</v>
       </c>
       <c r="C1041">
@@ -12016,7 +12013,7 @@
       <c r="A1042" s="1">
         <v>46051</v>
       </c>
-      <c r="B1042" s="7" t="s">
+      <c r="B1042" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1042">
@@ -12027,7 +12024,7 @@
       <c r="A1043" s="1">
         <v>46051</v>
       </c>
-      <c r="B1043" s="8" t="s">
+      <c r="B1043" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1043">
@@ -12038,7 +12035,7 @@
       <c r="A1044" s="1">
         <v>46051</v>
       </c>
-      <c r="B1044" s="6" t="s">
+      <c r="B1044" t="s">
         <v>9</v>
       </c>
       <c r="C1044">
@@ -12049,7 +12046,7 @@
       <c r="A1045" s="1">
         <v>46052</v>
       </c>
-      <c r="B1045" s="7" t="s">
+      <c r="B1045" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1045">
@@ -12060,7 +12057,7 @@
       <c r="A1046" s="1">
         <v>46052</v>
       </c>
-      <c r="B1046" s="8" t="s">
+      <c r="B1046" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1046">
@@ -12071,7 +12068,7 @@
       <c r="A1047" s="1">
         <v>46052</v>
       </c>
-      <c r="B1047" s="6" t="s">
+      <c r="B1047" t="s">
         <v>9</v>
       </c>
       <c r="C1047">
@@ -12082,7 +12079,7 @@
       <c r="A1048" s="1">
         <v>46055</v>
       </c>
-      <c r="B1048" s="7" t="s">
+      <c r="B1048" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1048">
@@ -12093,7 +12090,7 @@
       <c r="A1049" s="1">
         <v>46055</v>
       </c>
-      <c r="B1049" s="8" t="s">
+      <c r="B1049" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1049">
@@ -12104,7 +12101,7 @@
       <c r="A1050" s="1">
         <v>46055</v>
       </c>
-      <c r="B1050" s="6" t="s">
+      <c r="B1050" t="s">
         <v>9</v>
       </c>
       <c r="C1050">
@@ -12115,7 +12112,7 @@
       <c r="A1051" s="1">
         <v>46056</v>
       </c>
-      <c r="B1051" s="7" t="s">
+      <c r="B1051" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1051">
@@ -12126,7 +12123,7 @@
       <c r="A1052" s="1">
         <v>46056</v>
       </c>
-      <c r="B1052" s="8" t="s">
+      <c r="B1052" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1052">
@@ -12137,7 +12134,7 @@
       <c r="A1053" s="1">
         <v>46056</v>
       </c>
-      <c r="B1053" s="6" t="s">
+      <c r="B1053" t="s">
         <v>9</v>
       </c>
       <c r="C1053">
@@ -12148,7 +12145,7 @@
       <c r="A1054" s="1">
         <v>46057</v>
       </c>
-      <c r="B1054" s="7" t="s">
+      <c r="B1054" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1054">
@@ -12159,7 +12156,7 @@
       <c r="A1055" s="1">
         <v>46057</v>
       </c>
-      <c r="B1055" s="8" t="s">
+      <c r="B1055" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1055">
@@ -12170,7 +12167,7 @@
       <c r="A1056" s="1">
         <v>46057</v>
       </c>
-      <c r="B1056" s="6" t="s">
+      <c r="B1056" t="s">
         <v>9</v>
       </c>
       <c r="C1056">
@@ -12181,7 +12178,7 @@
       <c r="A1057" s="1">
         <v>46058</v>
       </c>
-      <c r="B1057" s="7" t="s">
+      <c r="B1057" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1057">
@@ -12192,7 +12189,7 @@
       <c r="A1058" s="1">
         <v>46058</v>
       </c>
-      <c r="B1058" s="8" t="s">
+      <c r="B1058" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1058">
@@ -12203,7 +12200,7 @@
       <c r="A1059" s="1">
         <v>46058</v>
       </c>
-      <c r="B1059" s="6" t="s">
+      <c r="B1059" t="s">
         <v>9</v>
       </c>
       <c r="C1059">
@@ -12214,7 +12211,7 @@
       <c r="A1060" s="1">
         <v>46059</v>
       </c>
-      <c r="B1060" s="7" t="s">
+      <c r="B1060" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1060">
@@ -12225,7 +12222,7 @@
       <c r="A1061" s="1">
         <v>46059</v>
       </c>
-      <c r="B1061" s="8" t="s">
+      <c r="B1061" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1061">
@@ -12236,7 +12233,7 @@
       <c r="A1062" s="1">
         <v>46059</v>
       </c>
-      <c r="B1062" s="6" t="s">
+      <c r="B1062" t="s">
         <v>9</v>
       </c>
       <c r="C1062">
@@ -12247,7 +12244,7 @@
       <c r="A1063" s="1">
         <v>46062</v>
       </c>
-      <c r="B1063" s="7" t="s">
+      <c r="B1063" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1063">
@@ -12258,7 +12255,7 @@
       <c r="A1064" s="1">
         <v>46062</v>
       </c>
-      <c r="B1064" s="8" t="s">
+      <c r="B1064" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1064">
@@ -12269,7 +12266,7 @@
       <c r="A1065" s="1">
         <v>46062</v>
       </c>
-      <c r="B1065" s="6" t="s">
+      <c r="B1065" t="s">
         <v>9</v>
       </c>
       <c r="C1065">
@@ -12280,7 +12277,7 @@
       <c r="A1066" s="1">
         <v>46063</v>
       </c>
-      <c r="B1066" s="7" t="s">
+      <c r="B1066" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1066">
@@ -12291,7 +12288,7 @@
       <c r="A1067" s="1">
         <v>46063</v>
       </c>
-      <c r="B1067" s="8" t="s">
+      <c r="B1067" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1067">
@@ -12302,7 +12299,7 @@
       <c r="A1068" s="1">
         <v>46063</v>
       </c>
-      <c r="B1068" s="6" t="s">
+      <c r="B1068" t="s">
         <v>9</v>
       </c>
       <c r="C1068">
@@ -12313,7 +12310,7 @@
       <c r="A1069" s="1">
         <v>46064</v>
       </c>
-      <c r="B1069" s="7" t="s">
+      <c r="B1069" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1069">
@@ -12324,7 +12321,7 @@
       <c r="A1070" s="1">
         <v>46064</v>
       </c>
-      <c r="B1070" s="8" t="s">
+      <c r="B1070" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1070">
@@ -12335,7 +12332,7 @@
       <c r="A1071" s="1">
         <v>46064</v>
       </c>
-      <c r="B1071" s="6" t="s">
+      <c r="B1071" t="s">
         <v>9</v>
       </c>
       <c r="C1071">
@@ -12346,7 +12343,7 @@
       <c r="A1072" s="1">
         <v>46065</v>
       </c>
-      <c r="B1072" s="7" t="s">
+      <c r="B1072" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1072">
@@ -12357,7 +12354,7 @@
       <c r="A1073" s="1">
         <v>46065</v>
       </c>
-      <c r="B1073" s="8" t="s">
+      <c r="B1073" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1073">
@@ -12368,7 +12365,7 @@
       <c r="A1074" s="1">
         <v>46065</v>
       </c>
-      <c r="B1074" s="6" t="s">
+      <c r="B1074" t="s">
         <v>9</v>
       </c>
       <c r="C1074">
@@ -12379,7 +12376,7 @@
       <c r="A1075" s="1">
         <v>46066</v>
       </c>
-      <c r="B1075" s="7" t="s">
+      <c r="B1075" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1075">
@@ -12390,7 +12387,7 @@
       <c r="A1076" s="1">
         <v>46066</v>
       </c>
-      <c r="B1076" s="8" t="s">
+      <c r="B1076" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1076">
@@ -12401,7 +12398,7 @@
       <c r="A1077" s="1">
         <v>46066</v>
       </c>
-      <c r="B1077" s="6" t="s">
+      <c r="B1077" t="s">
         <v>9</v>
       </c>
       <c r="C1077">
@@ -12412,7 +12409,7 @@
       <c r="A1078" s="1">
         <v>46069</v>
       </c>
-      <c r="B1078" s="7" t="s">
+      <c r="B1078" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1078">
@@ -12423,7 +12420,7 @@
       <c r="A1079" s="1">
         <v>46069</v>
       </c>
-      <c r="B1079" s="8" t="s">
+      <c r="B1079" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1079">
@@ -12434,7 +12431,7 @@
       <c r="A1080" s="1">
         <v>46069</v>
       </c>
-      <c r="B1080" s="6" t="s">
+      <c r="B1080" t="s">
         <v>9</v>
       </c>
       <c r="C1080">
@@ -12445,7 +12442,7 @@
       <c r="A1081" s="1">
         <v>46070</v>
       </c>
-      <c r="B1081" s="7" t="s">
+      <c r="B1081" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1081">
@@ -12456,7 +12453,7 @@
       <c r="A1082" s="1">
         <v>46070</v>
       </c>
-      <c r="B1082" s="8" t="s">
+      <c r="B1082" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1082">
@@ -12467,7 +12464,7 @@
       <c r="A1083" s="1">
         <v>46070</v>
       </c>
-      <c r="B1083" s="6" t="s">
+      <c r="B1083" t="s">
         <v>9</v>
       </c>
       <c r="C1083">
@@ -12478,7 +12475,7 @@
       <c r="A1084" s="1">
         <v>46071</v>
       </c>
-      <c r="B1084" s="7" t="s">
+      <c r="B1084" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1084">
@@ -12489,7 +12486,7 @@
       <c r="A1085" s="1">
         <v>46071</v>
       </c>
-      <c r="B1085" s="8" t="s">
+      <c r="B1085" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1085">
@@ -12500,7 +12497,7 @@
       <c r="A1086" s="1">
         <v>46071</v>
       </c>
-      <c r="B1086" s="6" t="s">
+      <c r="B1086" t="s">
         <v>9</v>
       </c>
       <c r="C1086">
@@ -12511,7 +12508,7 @@
       <c r="A1087" s="1">
         <v>46073</v>
       </c>
-      <c r="B1087" s="7" t="s">
+      <c r="B1087" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1087">
@@ -12522,7 +12519,7 @@
       <c r="A1088" s="1">
         <v>46073</v>
       </c>
-      <c r="B1088" s="8" t="s">
+      <c r="B1088" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1088">
@@ -12533,7 +12530,7 @@
       <c r="A1089" s="1">
         <v>46073</v>
       </c>
-      <c r="B1089" s="6" t="s">
+      <c r="B1089" t="s">
         <v>9</v>
       </c>
       <c r="C1089">
@@ -12544,7 +12541,7 @@
       <c r="A1090" s="1">
         <v>46076</v>
       </c>
-      <c r="B1090" s="7" t="s">
+      <c r="B1090" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1090">
@@ -12555,7 +12552,7 @@
       <c r="A1091" s="1">
         <v>46076</v>
       </c>
-      <c r="B1091" s="8" t="s">
+      <c r="B1091" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1091">
@@ -12566,7 +12563,7 @@
       <c r="A1092" s="1">
         <v>46076</v>
       </c>
-      <c r="B1092" s="6" t="s">
+      <c r="B1092" t="s">
         <v>9</v>
       </c>
       <c r="C1092">
@@ -12577,7 +12574,7 @@
       <c r="A1093" s="1">
         <v>46077</v>
       </c>
-      <c r="B1093" s="7" t="s">
+      <c r="B1093" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1093">
@@ -12588,7 +12585,7 @@
       <c r="A1094" s="1">
         <v>46077</v>
       </c>
-      <c r="B1094" s="8" t="s">
+      <c r="B1094" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1094">
@@ -12599,7 +12596,7 @@
       <c r="A1095" s="1">
         <v>46077</v>
       </c>
-      <c r="B1095" s="6" t="s">
+      <c r="B1095" t="s">
         <v>9</v>
       </c>
       <c r="C1095">
@@ -12610,7 +12607,7 @@
       <c r="A1096" s="1">
         <v>46078</v>
       </c>
-      <c r="B1096" s="7" t="s">
+      <c r="B1096" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1096">
@@ -12621,7 +12618,7 @@
       <c r="A1097" s="1">
         <v>46078</v>
       </c>
-      <c r="B1097" s="8" t="s">
+      <c r="B1097" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1097">
@@ -12632,7 +12629,7 @@
       <c r="A1098" s="1">
         <v>46078</v>
       </c>
-      <c r="B1098" s="6" t="s">
+      <c r="B1098" t="s">
         <v>9</v>
       </c>
       <c r="C1098">
@@ -12643,7 +12640,7 @@
       <c r="A1099" s="1">
         <v>46079</v>
       </c>
-      <c r="B1099" s="7" t="s">
+      <c r="B1099" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1099">
@@ -12654,7 +12651,7 @@
       <c r="A1100" s="1">
         <v>46079</v>
       </c>
-      <c r="B1100" s="8" t="s">
+      <c r="B1100" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1100">
@@ -12665,7 +12662,7 @@
       <c r="A1101" s="1">
         <v>46079</v>
       </c>
-      <c r="B1101" s="6" t="s">
+      <c r="B1101" t="s">
         <v>9</v>
       </c>
       <c r="C1101">
@@ -12676,7 +12673,7 @@
       <c r="A1102" s="1">
         <v>46080</v>
       </c>
-      <c r="B1102" s="7" t="s">
+      <c r="B1102" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1102">
@@ -12687,7 +12684,7 @@
       <c r="A1103" s="1">
         <v>46080</v>
       </c>
-      <c r="B1103" s="8" t="s">
+      <c r="B1103" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1103">
@@ -12698,7 +12695,7 @@
       <c r="A1104" s="1">
         <v>46080</v>
       </c>
-      <c r="B1104" s="6" t="s">
+      <c r="B1104" t="s">
         <v>9</v>
       </c>
       <c r="C1104">
@@ -12709,7 +12706,7 @@
       <c r="A1105" s="1">
         <v>46083</v>
       </c>
-      <c r="B1105" s="7" t="s">
+      <c r="B1105" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1105">
@@ -12720,7 +12717,7 @@
       <c r="A1106" s="1">
         <v>46083</v>
       </c>
-      <c r="B1106" s="8" t="s">
+      <c r="B1106" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1106">
@@ -12731,7 +12728,7 @@
       <c r="A1107" s="1">
         <v>46083</v>
       </c>
-      <c r="B1107" s="6" t="s">
+      <c r="B1107" t="s">
         <v>9</v>
       </c>
       <c r="C1107">
@@ -12742,7 +12739,7 @@
       <c r="A1108" s="1">
         <v>46084</v>
       </c>
-      <c r="B1108" s="7" t="s">
+      <c r="B1108" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1108">
@@ -12753,7 +12750,7 @@
       <c r="A1109" s="1">
         <v>46084</v>
       </c>
-      <c r="B1109" s="8" t="s">
+      <c r="B1109" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1109">
@@ -12764,7 +12761,7 @@
       <c r="A1110" s="1">
         <v>46084</v>
       </c>
-      <c r="B1110" s="6" t="s">
+      <c r="B1110" t="s">
         <v>9</v>
       </c>
       <c r="C1110">
@@ -12775,7 +12772,7 @@
       <c r="A1111" s="1">
         <v>46085</v>
       </c>
-      <c r="B1111" s="7" t="s">
+      <c r="B1111" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C1111">
@@ -12786,7 +12783,7 @@
       <c r="A1112" s="1">
         <v>46085</v>
       </c>
-      <c r="B1112" s="8" t="s">
+      <c r="B1112" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1112">
@@ -12797,7 +12794,7 @@
       <c r="A1113" s="1">
         <v>46085</v>
       </c>
-      <c r="B1113" s="6" t="s">
+      <c r="B1113" t="s">
         <v>9</v>
       </c>
       <c r="C1113">
